--- a/medford_lor_kombayny.xlsx
+++ b/medford_lor_kombayny.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ЛОР-комбайны для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Heine — всего 20 позиций.</t>
+          <t>ЛОР-комбайны для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Heine.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_lor_kombayny.xlsx
+++ b/medford_lor_kombayny.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать лОР-комбайны для клиники?</t>
+          <t>Что входит в ЛОР-комбайн?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Класс, Страна производства, Производитель, Шум, дБ). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Базовая комплектация включает три режима: аспирация для вакуумного удаления отделяемого, промывание с подогревом жидкости и компрессорный модуль для орошения. Добавляют систему хранения со встроенными ящиками, подогрев зеркал и инструментов, лотки для отходов. Опционально — эндоскопическая система с камерой и монитором, источник света, микроскоп.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Чем различаются классы ЛОР-установок?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Установки делят на средний, высокий и экспертный класс. Средний класс покрывает базовый приём, высокий и экспертный добавляют модули, расширенную комплектацию и опции вроде эндоскопии и микроскопа. Класс выбирают исходя из потока пациентов, спектра процедур и планируемого оснащения кабинета.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Нужна ли эндоскопия в составе комбайна?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Heine. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Если на рабочем месте планируется видеоэндоскопия, выбирают конфигурацию со стойкой и гнёздами для эндоскопов, камерой, монитором и источником света — например, Элема-Н ЛК1Э. Для базового приёма без видеоэндоскопии достаточно установки с аспирацией, промыванием и компрессором.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Какая мощность аспиратора нужна?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Мощность аспиратора указывают в кПа. У HEINEMANN Modula — до -80/90 кПа при потоке 40–60 л/мин. Достаточная мощность обеспечивает эффективное удаление отделяемого при манипуляциях. Конкретное значение подбирают под характер процедур; параметры указаны в характеристиках модели.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Российский или импортный ЛОР-комбайн выбрать?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>В каталоге есть российские установки (Элема-Н, Zerts) и импортные (Dixion, HEINEMANN, MEGA MEDICAL, MedStar). Российские модели обычно проще в сервисе и снабжении запчастями, импортные экспертного класса предлагают расширенные модули. Выбор зависит от бюджета, требований к комплектации и доступности обслуживания.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Что входит в ЛОР комбайн?</t>
+          <t>Что такое модульная ЛОР-установка?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Модульная установка позволяет наращивать функции отдельными блоками. Например, у Zerts есть модуль подогрева инструмента ZERTS Hot с контролем температуры и защитой от перегрева и мобильный модуль ZERTS MOBIL. Такой подход даёт собрать конфигурацию под конкретные задачи кабинета и расширять её позже.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Какова цена свеклоуборочного комбайна?</t>
+          <t>Насколько шумной бывает установка?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Уровень шума зависит от модели; у российской Элема-Н ЛК1 он составляет 70 дБ. Для комфортного приёма и пациента, и врача уровень шума имеет значение, особенно при длительной работе аспиратора и компрессора. Значение уточняют по характеристикам конкретной модели.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1264,6 +1264,44 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Нужно ли регистрационное удостоверение Росздравнадзора?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Да. ЛОР-комбайн — медицинское изделие, его применение в клинике в РФ требует действующего регистрационного удостоверения Росздравнадзора. Перед закупкой запросите документ на конкретную модель и комплектацию у поставщика и убедитесь в его актуальности.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>lor_kombayny</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2148,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ЛОР-комбайны для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Heine.</t>
+          <t>ЛОР-комбайны (ЛОР-установки) — рабочее место оториноларинголога, объединяющее аспирацию, промывание с подогревом жидкости, компрессорный модуль для орошения и систему хранения инструментов в одном корпусе. В каталоге представлены модели Dixion, MEGA MEDICAL, Элема-Н, HEINEMANN, Zerts (ZERTS), MedStar среднего, высокого и экспертного классов. Российские установки Элема-Н несут корпус из нержавеющей стали, время непрерывной работы 8 часов и ёмкость для промывающей жидкости 3 л. Старшие конфигурации дополняются стойкой и гнёздами для эндоскопов, модулями подогрева инструмента и ящиков.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2470,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>ЛОР-комбайны в каталоге по классам</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2758,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое лОР-комбайны</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4418,231 +4456,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — ЛОР-комбайны в каталоге по классам</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Класс</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Примеры моделей</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Класс</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Страна производства</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Производитель</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Шум, дБ</t>
+          <t>Назначение</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>ЛОР-установка Dixion ST-E500</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Dixion ST-E500, ST-E600, Элема-Н ЛК1, Zerts ZET, ZERTS Profy</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Базовый приём с аспирацией, промыванием и орошением</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>ЛОР-установка MEGA MEDICAL Mobile NET-1100</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Dixion ST-E900, HEINEMANN Modula-Europa, MEGA MEDICAL NET-3000D, MedStar Grand-2000S</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Расширенная комплектация, опции эндоскопии</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ЛОР-установка Элема-Н ЛК1 (базовая модификация)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
+          <t>Экспертный</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>HEINEMANN Modula-Europa Paris Duo</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>67415</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>ЛОР-установка Элема-Н ЛК1М (модификация с модулем ящиков)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>67415</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>ЛОР-установка HEINEMANN Modula</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Heine</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>ЛОР-комбайн Zerts ZET Plus</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>67371</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Максимальная комплектация для сложного приёма</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4654,7 +4553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4980,12 +4879,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите класс установки</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается лОР-комбайны: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>ЛОР-комбайны делят на средний, высокий и экспертный класс. Средний класс (Dixion ST-E500, Zerts ZET) покрывает базовый приём, высокий (Dixion ST-E900, HEINEMANN Modula-Europa) и экспертный (HEINEMANN Modula-Europa Paris Duo) добавляют модули и расширенную комплектацию. Класс подбирают под поток пациентов и спектр процедур.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5025,12 +4924,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Проверьте состав рабочих модулей</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Базовые режимы — аспирация, промывание с подогревом жидкости, компрессорный модуль для орошения. Убедитесь, что нужные модули входят в комплектацию выбранной конфигурации. Модульные установки Zerts позволяют добавить подогрев инструмента (ZERTS Hot) или мобильный модуль (ZERTS MOBIL).</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5070,12 +4969,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Оцените параметры аспирации и промывания</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Класс, Страна производства, Производитель, Шум, дБ. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Мощность аспиратора указывают в кПа: у HEINEMANN Modula — до -80/90 кПа (40–60 л/мин). Объём ёмкости для промывающей жидкости у Элема-Н — 3 л, время непрерывной работы — 8 часов. Эти параметры определяют, насколько комфортно вести длительный приём без пауз.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5115,12 +5014,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Решите вопрос эндоскопии</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Heine.</t>
+          <t>Часть установок комплектуется стойкой и гнёздами для эндоскопов (Элема-Н ЛК1Э), эндоскопической системой с камерой, монитором, источником света и микроскопом. Если планируете видеоэндоскопию на рабочем месте, выбирайте конфигурацию с соответствующими опциями сразу.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5160,12 +5059,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Учтите систему хранения и подогрев</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Встроенные ящики для инструментов, подогрев зеркал и инструментов, лотки для отходов ускоряют приём. Модуль подогрева (ZERTS Hot) контролирует температуру инструмента с защитой от перегрева. Столешница из закалённого стекла у Элема-Н упрощает обработку рабочей поверхности.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5205,12 +5104,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Проверьте материалы, шум и документы</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Корпус из нержавеющей стали и стали с полимерным покрытием устойчив к обработке. Уровень шума у Элема-Н — 70 дБ. Убедитесь в наличии действующего регистрационного удостоверения Росздравнадзора и уточните доступность сервиса и запчастей для выбранного бренда.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5260,7 +5159,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>ЛОР-комбайны подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Heine. При выборе обращают внимание на класс, страна производства, производитель, шум, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>ЛОР-комбайн покупают на годы, поэтому первым делом смотрю на состав рабочих модулей: аспирация, промывание с подогревом, компрессор для орошения — это база. Дальше — класс установки и то, нужна ли эндоскопическая стойка с гнёздами под эндоскопы и подогрев инструмента. Российские модели вроде Элема-Н дают предсказуемый сервис и запчасти. Отдельно оцениваю мощность аспиратора в кПа, объём ёмкости для промывающей жидкости и время непрерывной работы.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5544,13 +5443,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое лОР-комбайны</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>ЛОР-комбайны — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Heine. Подберём вариант под задачи вашего отделения.</t>
+          <t>ЛОР-комбайн (ЛОР-установка) — интегрированное рабочее место оториноларинголога с тремя базовыми режимами: аспирация, промывание с подогревом жидкости и компрессорный модуль для орошения. В комплектацию входят система хранения с подогревом зеркал и инструментов, лотки для отходов; опционально — эндоскопия с камерой и монитором, источник света, микроскоп. Установки различают по классу: средний, высокий, экспертный. В каталоге модели Dixion, MEGA MEDICAL, Элема-Н, HEINEMANN, Zerts и MedStar; выбор ведут по классу, комплектации и совместимости с оснащением кабинета.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5587,13 +5486,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое ЛОР-комбайн</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Класс, Страна производства, Производитель, Шум, дБ), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>ЛОР-комбайн (ЛОР-установка) — интегрированное рабочее место оториноларинголога, объединяющее в одном корпусе основные функции приёма: аспирацию отделяемого, промывание с подогревом жидкости и компрессорный модуль для орошения. Установка организует инструменты и расходники, ускоряет подготовку к манипуляциям и создаёт эргономичное рабочее пространство для диагностики и лечения ЛОР-патологий.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5630,13 +5529,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Базовая комплектация и модули</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>В базовую комплектацию входят аспиратор и ирригатор, компрессорный модуль для распыления лекарственных средств, система хранения со встроенными ящиками, подогрев зеркал и инструментов, лотки для отходов. Опционально устанавливают эндоскопическую систему с камерой и монитором, источник света и микроскоп. Модульные установки позволяют наращивать функции отдельными блоками.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5673,13 +5572,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Классы установок</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>ЛОР-комбайны различают по классу: средний, высокий и экспертный. Средний класс покрывает базовый приём, высокий и экспертный добавляют расширенную комплектацию, эндоскопию и дополнительные модули. В каталоге представлены Dixion ST-E500/E600/E900, MEGA MEDICAL, Элема-Н ЛК1, HEINEMANN Modula и Modula-Europa, Zerts ZET, MedStar разных классов.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5696,6 +5595,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Материалы и эксплуатация</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Корпуса установок выполняют из нержавеющей стали и стали с полимерным покрытием, столешницы — из закалённого стекла, что упрощает санитарную обработку. Российская Элема-Н ЛК1 рассчитана на 8 часов непрерывной работы, несёт ёмкость для промывающей жидкости 3 л и автоклавируемые аспирационные банки. Уровень шума и материалы влияют на комфорт длительного приёма.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>lor_kombayny</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
